--- a/Excel/Amazon_Delivery_Analysis.xlsx
+++ b/Excel/Amazon_Delivery_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\donga\Documents\Amazon_Delivery_Analysis\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C01462-2330-4B6D-972F-05E2A17D263E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD9B1B9-8BC9-4E10-85D6-114F8DE25EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{0DAF1268-871B-4793-BF50-A73871AA9557}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -534,12 +534,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -568,3503 +562,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="490">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4091,6 +599,78 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -6146,45 +2726,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1"/>
-                </a:gs>
-                <a:gs pos="75000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="51000">
-                  <a:schemeClr val="accent1">
-                    <a:alpha val="75000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                    <a:alpha val="15000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6264,45 +2806,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2"/>
-                </a:gs>
-                <a:gs pos="75000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="51000">
-                  <a:schemeClr val="accent2">
-                    <a:alpha val="75000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                    <a:alpha val="15000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6382,45 +2886,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill flip="none" rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent3"/>
-                </a:gs>
-                <a:gs pos="75000">
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="51000">
-                  <a:schemeClr val="accent3">
-                    <a:alpha val="75000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                    <a:alpha val="15000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -9529,7 +5995,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="13356770" cy="7679374"/>
+          <a:ext cx="13356770" cy="7782369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9955,7 +6421,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="2400" b="1" baseline="0"/>
-            <a:t>  34</a:t>
+            <a:t>  75%</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="2400" b="1"/>
         </a:p>
@@ -10126,8 +6592,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>87085</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="22" name="Service_Type">
@@ -10150,7 +6616,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10204,8 +6670,8 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>55419</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="23" name="Month">
@@ -10228,7 +6694,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10459,7 +6925,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F8212D4-179E-4644-8E22-57F1C09F1A0C}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F8212D4-179E-4644-8E22-57F1C09F1A0C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="K2:L6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -10503,26 +6969,26 @@
     <dataField name="Sum of Delay_Days" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="416">
+    <format dxfId="9">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="415">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="414">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="413">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="412">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="411">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -10568,7 +7034,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15BF41C1-8BB3-4D04-8001-DD5719CA4E63}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" colHeaderCaption="Months">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15BF41C1-8BB3-4D04-8001-DD5719CA4E63}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" colHeaderCaption="Months">
   <location ref="D2:H6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -10629,51 +7095,51 @@
     <dataField name="Total Delays Days" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="41">
-    <format dxfId="461">
+    <format dxfId="50">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="460">
+    <format dxfId="49">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="459">
+    <format dxfId="48">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="458">
+    <format dxfId="47">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="457">
+    <format dxfId="46">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="456">
+    <format dxfId="45">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="455">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="454">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="453">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="452">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="451">
+    <format dxfId="40">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="450">
+    <format dxfId="39">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="449">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -10682,10 +7148,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="448">
+    <format dxfId="37">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="447">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -10694,7 +7160,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="446">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -10703,10 +7169,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="445">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="444">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2" selected="0">
@@ -10716,89 +7182,89 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="443">
+    <format dxfId="32">
       <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="442">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="441">
+    <format dxfId="30">
       <pivotArea grandRow="1" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="440">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="439">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="438">
+    <format dxfId="27">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="437">
+    <format dxfId="26">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="436">
+    <format dxfId="25">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="435">
+    <format dxfId="24">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="434">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="433">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="432">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="431">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="430">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="429">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="428">
+    <format dxfId="17">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="427">
+    <format dxfId="16">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="426">
+    <format dxfId="15">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="425">
+    <format dxfId="14">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="424">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="423">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="422">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="421">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -10930,15 +7396,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1D84D8A-4974-4F01-84BA-FAF5A34B800B}" name="raw" displayName="raw" ref="A1:F14" totalsRowShown="0" headerRowDxfId="489" dataDxfId="487" headerRowBorderDxfId="488" tableBorderDxfId="486" totalsRowBorderDxfId="485">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1D84D8A-4974-4F01-84BA-FAF5A34B800B}" name="raw" displayName="raw" ref="A1:F14" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
   <autoFilter ref="A1:F14" xr:uid="{A1D84D8A-4974-4F01-84BA-FAF5A34B800B}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8A29CCD5-6F7E-4194-A130-8405234CA197}" name="Record_id" dataDxfId="484"/>
-    <tableColumn id="2" xr3:uid="{5D0E7868-A5AB-49C2-9D1A-73ED2BACBC15}" name="Month" dataDxfId="483"/>
-    <tableColumn id="3" xr3:uid="{B521D67A-190C-4D16-BFBA-1A5EA14B3EC5}" name="Route_id" dataDxfId="482"/>
-    <tableColumn id="4" xr3:uid="{662D17C2-795F-4F0F-B604-FE07F25BC30D}" name="HUB" dataDxfId="481"/>
-    <tableColumn id="5" xr3:uid="{D6466A36-7FD4-4467-96B9-D88B3B66EF3B}" name="Promised_Days" dataDxfId="480"/>
-    <tableColumn id="6" xr3:uid="{C34E55EB-DA8D-4057-AC57-A1831D09BE43}" name="Actual_Days" dataDxfId="479"/>
+    <tableColumn id="1" xr3:uid="{8A29CCD5-6F7E-4194-A130-8405234CA197}" name="Record_id" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{5D0E7868-A5AB-49C2-9D1A-73ED2BACBC15}" name="Month" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{B521D67A-190C-4D16-BFBA-1A5EA14B3EC5}" name="Route_id" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{662D17C2-795F-4F0F-B604-FE07F25BC30D}" name="HUB" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{D6466A36-7FD4-4467-96B9-D88B3B66EF3B}" name="Promised_Days" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{C34E55EB-DA8D-4057-AC57-A1831D09BE43}" name="Actual_Days" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10948,31 +7414,31 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD5F6343-B4F7-4DB0-9AA6-41BC650E5CF2}" name="lookup" displayName="lookup" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5" xr:uid="{FD5F6343-B4F7-4DB0-9AA6-41BC650E5CF2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{57FB891F-8D48-4023-B5DE-904388E22344}" name="Route_id" dataDxfId="478"/>
-    <tableColumn id="2" xr3:uid="{942D2EB0-B2ED-40DA-90DB-8E8709F46EED}" name="Route" dataDxfId="477"/>
-    <tableColumn id="3" xr3:uid="{8AF79C35-9716-4B20-9718-D9D75D75E421}" name="Service_Type" dataDxfId="476"/>
+    <tableColumn id="1" xr3:uid="{57FB891F-8D48-4023-B5DE-904388E22344}" name="Route_id" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{942D2EB0-B2ED-40DA-90DB-8E8709F46EED}" name="Route" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{8AF79C35-9716-4B20-9718-D9D75D75E421}" name="Service_Type" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9E89A22-B85E-4709-8DE7-C6BD1B546840}" name="clean" displayName="clean" ref="A1:I13" totalsRowShown="0" headerRowDxfId="475" dataDxfId="473" headerRowBorderDxfId="474" tableBorderDxfId="472" totalsRowBorderDxfId="471">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9E89A22-B85E-4709-8DE7-C6BD1B546840}" name="clean" displayName="clean" ref="A1:I13" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="A1:I13" xr:uid="{C9E89A22-B85E-4709-8DE7-C6BD1B546840}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{03D83C69-E09B-4D6F-A931-9215831AB485}" name="Record_id" dataDxfId="470"/>
-    <tableColumn id="2" xr3:uid="{811DAFCB-B0E6-4838-BC7A-CC758E28DBCC}" name="Month" dataDxfId="469"/>
-    <tableColumn id="3" xr3:uid="{CC393245-C6D1-4AFF-954A-DC0D2A8983F9}" name="Route_id" dataDxfId="468"/>
-    <tableColumn id="4" xr3:uid="{1A3C55CE-E183-4063-9FF1-7465D34EFF0D}" name="HUB" dataDxfId="467"/>
-    <tableColumn id="5" xr3:uid="{923B9AF3-B9F8-4914-8B69-887E5300DF0B}" name="Promised_Days" dataDxfId="466"/>
-    <tableColumn id="6" xr3:uid="{F11348C1-CC7F-487F-A893-847A915D152E}" name="Actual_Days" dataDxfId="465"/>
-    <tableColumn id="7" xr3:uid="{C1A6F8F5-8172-4687-9F08-BF84909AE77E}" name="Service_Type" dataDxfId="464">
+    <tableColumn id="1" xr3:uid="{03D83C69-E09B-4D6F-A931-9215831AB485}" name="Record_id" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{811DAFCB-B0E6-4838-BC7A-CC758E28DBCC}" name="Month" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{CC393245-C6D1-4AFF-954A-DC0D2A8983F9}" name="Route_id" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{1A3C55CE-E183-4063-9FF1-7465D34EFF0D}" name="HUB" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{923B9AF3-B9F8-4914-8B69-887E5300DF0B}" name="Promised_Days" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{F11348C1-CC7F-487F-A893-847A915D152E}" name="Actual_Days" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{C1A6F8F5-8172-4687-9F08-BF84909AE77E}" name="Service_Type" dataDxfId="53">
       <calculatedColumnFormula>INDEX(lookup[Service_Type],MATCH(C2,lookup[Route_id],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8751EC36-D8FC-47C2-B3FF-CF08C5591548}" name="Delay_Days" dataDxfId="463">
+    <tableColumn id="8" xr3:uid="{8751EC36-D8FC-47C2-B3FF-CF08C5591548}" name="Delay_Days" dataDxfId="52">
       <calculatedColumnFormula>MAX(clean[[#This Row],[Actual_Days]]-clean[[#This Row],[Promised_Days]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{CFD81865-F0CA-4CAB-B47B-6D5A29E4FC98}" name="Route" dataDxfId="462">
+    <tableColumn id="9" xr3:uid="{CFD81865-F0CA-4CAB-B47B-6D5A29E4FC98}" name="Route" dataDxfId="51">
       <calculatedColumnFormula>INDEX(lookup[Route],MATCH(C2,lookup[Route_id],0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10981,11 +7447,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE9C4A1E-4661-4BD4-9138-57BA859C3399}" name="Table4" displayName="Table4" ref="A2:B5" totalsRowShown="0" dataDxfId="420" tableBorderDxfId="419">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE9C4A1E-4661-4BD4-9138-57BA859C3399}" name="Table4" displayName="Table4" ref="A2:B5" totalsRowShown="0" dataDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A2:B5" xr:uid="{CE9C4A1E-4661-4BD4-9138-57BA859C3399}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{44F94961-F5CB-42EC-8921-62F97D86A89C}" name="HUB" dataDxfId="418"/>
-    <tableColumn id="2" xr3:uid="{246B343D-8075-45AE-A94E-AAAF502EDFAA}" name="Delay_Days" dataDxfId="417">
+    <tableColumn id="1" xr3:uid="{44F94961-F5CB-42EC-8921-62F97D86A89C}" name="HUB" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{246B343D-8075-45AE-A94E-AAAF502EDFAA}" name="Delay_Days" dataDxfId="0">
       <calculatedColumnFormula>SUMIF(clean[HUB], Table4[[#This Row],[HUB]], clean[Delay_Days])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12236,10 +8702,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="51"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -12254,13 +8720,13 @@
       <c r="E2" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="48"/>
-      <c r="K2" s="40" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="46"/>
+      <c r="K2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="43" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12278,19 +8744,19 @@
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="46" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="41">
+      <c r="L3" s="39">
         <v>8</v>
       </c>
     </row>
@@ -12311,16 +8777,16 @@
       <c r="F4" s="32">
         <v>3</v>
       </c>
-      <c r="G4" s="49">
+      <c r="G4" s="47">
         <v>8</v>
       </c>
       <c r="H4" s="33">
         <v>12</v>
       </c>
-      <c r="K4" s="43" t="s">
+      <c r="K4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="41">
+      <c r="L4" s="39">
         <v>9</v>
       </c>
     </row>
@@ -12341,16 +8807,16 @@
       <c r="F5" s="34">
         <v>6</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="48">
         <v>9</v>
       </c>
       <c r="H5" s="35">
         <v>22</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="39">
         <v>17</v>
       </c>
     </row>
@@ -12364,16 +8830,16 @@
       <c r="F6" s="36">
         <v>9</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="49">
         <v>17</v>
       </c>
       <c r="H6" s="37">
         <v>34</v>
       </c>
-      <c r="K6" s="44" t="s">
+      <c r="K6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="40">
         <v>34</v>
       </c>
     </row>
